--- a/master/result/37_修仙之路_从凡人到女帝/37_修仙之路_从凡人到女帝.xlsx
+++ b/master/result/37_修仙之路_从凡人到女帝/37_修仙之路_从凡人到女帝.xlsx
@@ -397,357 +397,451 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:D31"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>flavor</v>
       </c>
       <c r="B2" t="str">
-        <v>flavor</v>
+        <v>/flavor/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>风味</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>geology</v>
       </c>
       <c r="B3" t="str">
-        <v>geology</v>
+        <v>/geology/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>地质学</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>stroll</v>
       </c>
       <c r="B4" t="str">
-        <v>stroll</v>
+        <v>/stroll/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>漫步</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>queue</v>
       </c>
       <c r="B5" t="str">
-        <v>queue</v>
+        <v>/queue/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>排队</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>brother</v>
       </c>
       <c r="B6" t="str">
-        <v>brother</v>
+        <v>/brother/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>兄弟</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>injury</v>
       </c>
       <c r="B7" t="str">
-        <v>injury</v>
+        <v>/injury/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>伤害</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>rare</v>
       </c>
       <c r="B8" t="str">
-        <v>rare</v>
+        <v>/rare/</v>
       </c>
       <c r="C8" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>稀有的</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>shallow</v>
       </c>
       <c r="B9" t="str">
-        <v>shallow</v>
+        <v>/shallow/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>浅的</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>congratulation</v>
       </c>
       <c r="B10" t="str">
-        <v>congratulation</v>
+        <v>/kənˌɡrætʃuˈleɪʃn/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>祝贺</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>timid</v>
       </c>
       <c r="B11" t="str">
-        <v>timid</v>
+        <v>/timid/</v>
       </c>
       <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>胆怯的</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>inventory</v>
       </c>
       <c r="B12" t="str">
-        <v>inventory</v>
+        <v>/inventory/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>存货</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>stale</v>
       </c>
       <c r="B13" t="str">
-        <v>stale</v>
+        <v>/stale/</v>
       </c>
       <c r="C13" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>变质的</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>clarity</v>
       </c>
       <c r="B14" t="str">
-        <v>clarity</v>
+        <v>/clarity/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>清晰</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>ladder</v>
       </c>
       <c r="B15" t="str">
-        <v>ladder</v>
+        <v>/ladder/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>梯子</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>blossom</v>
       </c>
       <c r="B16" t="str">
-        <v>blossom</v>
+        <v>/blossom/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>花</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>premium</v>
       </c>
       <c r="B17" t="str">
-        <v>premium</v>
+        <v>/premium/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>额外费用</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>obey</v>
       </c>
       <c r="B18" t="str">
-        <v>obey</v>
+        <v>/əʊˈbeɪ/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>服从</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>spiral</v>
       </c>
       <c r="B19" t="str">
-        <v>spiral</v>
+        <v>/spiral/</v>
       </c>
       <c r="C19" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>螺旋</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>pity</v>
       </c>
       <c r="B20" t="str">
-        <v>pity</v>
+        <v>/ˈpɪti/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>可怜</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>battle</v>
       </c>
       <c r="B21" t="str">
-        <v>battle</v>
+        <v>/ˈbætəl/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>战斗</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>our</v>
       </c>
       <c r="B22" t="str">
-        <v>our</v>
+        <v>/our/</v>
       </c>
       <c r="C22" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D22" t="str">
         <v>我们的</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>superiority</v>
       </c>
       <c r="B23" t="str">
-        <v>superiority</v>
+        <v>/superiority/</v>
       </c>
       <c r="C23" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>优越</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>pitch</v>
       </c>
       <c r="B24" t="str">
-        <v>pitch</v>
+        <v>/pitch/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>投掷</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>orange</v>
       </c>
       <c r="B25" t="str">
-        <v>orange</v>
+        <v>/orange/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>橙子</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>wretched</v>
       </c>
       <c r="B26" t="str">
-        <v>wretched</v>
+        <v>/wretched/</v>
       </c>
       <c r="C26" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D26" t="str">
         <v>可怜的</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>particular</v>
       </c>
       <c r="B27" t="str">
-        <v>particular</v>
+        <v>/particular/</v>
       </c>
       <c r="C27" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D27" t="str">
         <v>特殊的</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>sacrifice</v>
       </c>
       <c r="B28" t="str">
-        <v>sacrifice</v>
+        <v>/sacrifice/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>牺牲</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>peaceful</v>
       </c>
       <c r="B29" t="str">
-        <v>peaceful</v>
+        <v>/peaceful/</v>
       </c>
       <c r="C29" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>和平的</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>elapse</v>
       </c>
       <c r="B30" t="str">
-        <v>elapse</v>
+        <v>/elapse/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>流逝</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>simplicity</v>
       </c>
       <c r="B31" t="str">
-        <v>simplicity</v>
+        <v>/simplicity/</v>
       </c>
       <c r="C31" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>简单</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D31"/>
   </ignoredErrors>
 </worksheet>
 </file>